--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98439</v>
+        <v>98440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98439</v>
+        <v>98440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98439</v>
+        <v>98440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98439</v>
+        <v>98440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98439</v>
+        <v>98440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104868</v>
+        <v>104869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98440</v>
+        <v>98445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98440</v>
+        <v>98445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98440</v>
+        <v>98445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98440</v>
+        <v>98445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98440</v>
+        <v>98445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136690266</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136690314</v>
       </c>
       <c r="B8" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98445</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98445</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98445</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98445</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98445</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98462</v>
+        <v>98466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98462</v>
+        <v>98466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98462</v>
+        <v>98466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98462</v>
+        <v>98466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98462</v>
+        <v>98466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98466</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98466</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98466</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98466</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98466</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136690266</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136690314</v>
       </c>
       <c r="B8" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98483</v>
+        <v>98485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98483</v>
+        <v>98485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98483</v>
+        <v>98485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98483</v>
+        <v>98485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98483</v>
+        <v>98485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136690266</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136690314</v>
       </c>
       <c r="B8" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -1262,11 +1262,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1376,11 +1372,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2026 artfynd.xlsx
+++ b/artfynd/A 36595-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136690386</v>
       </c>
       <c r="B2" t="n">
-        <v>98485</v>
+        <v>98488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136690446</v>
       </c>
       <c r="B3" t="n">
-        <v>98485</v>
+        <v>98488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -905,7 +905,7 @@
         <v>136690495</v>
       </c>
       <c r="B4" t="n">
-        <v>98485</v>
+        <v>98488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136690708</v>
       </c>
       <c r="B5" t="n">
-        <v>98485</v>
+        <v>98488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136690737</v>
       </c>
       <c r="B6" t="n">
-        <v>98485</v>
+        <v>98488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136690677</v>
       </c>
       <c r="B9" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
